--- a/tables/cva_study_metadata.xlsx
+++ b/tables/cva_study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/cva_analysis/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21AB16E-8DE5-4F4B-8098-870CE6B54DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604E3907-1A9A-6F4E-ACDC-F36B17D617D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37020" yWindow="5580" windowWidth="28040" windowHeight="17440" xr2:uid="{A6514CB6-B760-4041-B8A1-3AE3DE6C446D}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{A6514CB6-B760-4041-B8A1-3AE3DE6C446D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
     <t># of species</t>
   </si>
@@ -230,17 +230,17 @@
     <t>Atlantic marine mammals</t>
   </si>
   <si>
-    <t>US CVAs not included in our study</t>
-  </si>
-  <si>
     <t>South Atlantic</t>
+  </si>
+  <si>
+    <t>U.S.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -260,6 +260,13 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -292,11 +299,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57719DFA-98EC-A148-9BF2-FD782E15363C}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.1640625" customWidth="1"/>
@@ -779,7 +790,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6">
         <v>71</v>
@@ -907,77 +918,79 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="F13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="E13">
+      <c r="E16">
         <v>8.5</v>
       </c>
-      <c r="F13">
+      <c r="F16">
         <v>10</v>
       </c>
-      <c r="G13">
+      <c r="G16">
         <v>9</v>
       </c>
-      <c r="H13">
+      <c r="H16">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B17" t="s">
         <v>62</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C17" t="s">
         <v>16</v>
-      </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14">
-        <v>8.5</v>
-      </c>
-      <c r="F14">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>11</v>
-      </c>
-      <c r="H14">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17">
-        <v>28</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -986,174 +999,205 @@
         <v>8.5</v>
       </c>
       <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>11</v>
+      </c>
+      <c r="H17">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20">
+        <v>8.5</v>
+      </c>
+      <c r="F20">
         <v>10</v>
       </c>
-      <c r="G17">
+      <c r="G20">
         <v>13</v>
       </c>
-      <c r="H17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="H20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>29</v>
       </c>
-      <c r="C18">
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D21" t="s">
         <v>30</v>
-      </c>
-      <c r="E18">
-        <v>8.5</v>
-      </c>
-      <c r="F18">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>12</v>
-      </c>
-      <c r="H18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19">
-        <v>8.5</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>10</v>
-      </c>
-      <c r="H19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
-      </c>
-      <c r="G20">
-        <v>12</v>
-      </c>
-      <c r="H20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" t="s">
-        <v>17</v>
       </c>
       <c r="E21">
         <v>8.5</v>
       </c>
       <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>8.5</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24">
+        <v>8.5</v>
+      </c>
+      <c r="F24">
         <v>8</v>
       </c>
-      <c r="G21">
+      <c r="G24">
         <v>14</v>
       </c>
-      <c r="H21">
+      <c r="H24">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B31" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2" t="s">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2" t="s">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2">
         <v>6</v>
       </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2" t="s">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
